--- a/2026 南九州冬季聖誕自駕/travel_data_import.xlsx
+++ b/2026 南九州冬季聖誕自駕/travel_data_import.xlsx
@@ -22,6 +22,12 @@
     <t>🇯🇵 2026 家族南九州 7天6夜自駕深度探索之旅</t>
   </si>
   <si>
+    <t>🇯🇵 2026 南九州家族之旅 • 4人旅費分攤結算系統</t>
+  </si>
+  <si>
+    <t>💱 日幣匯率 (JPY➔TWD)</t>
+  </si>
+  <si>
     <t>動線總覽：熊本 ➔ 阿蘇火山 ➔ 黑川溫泉 ➔ 高千穗峽谷 ➔ 宮崎日南海岸 ➔ 鹿兒島・櫻島 ➔ 霧島神宮 ➔ 人吉 ➔ 熊本</t>
   </si>
   <si>
@@ -37,6 +43,9 @@
     <t>⚠️ 核心可行性提示</t>
   </si>
   <si>
+    <t>（可依即時牌告修改）</t>
+  </si>
+  <si>
     <t>7 天 6 夜（2026/12/22 二 ～ 12/28 一）</t>
   </si>
   <si>
@@ -46,9 +55,15 @@
     <t>熊本(1N) ➔ 黑川(1N) ➔ 宮崎(1N) ➔ 鹿兒島(2N) ➔ 熊本(1N)</t>
   </si>
   <si>
+    <t>📅 2026/12/22 ~ 12/28（7天6夜） ｜ 👥 家族成員 4 位 ｜ 💡 支援日幣/台幣雙幣自動折算與即時多方代墊平分</t>
+  </si>
+  <si>
     <t>冬季山區需租雪胎、高千穗划船提早預約、改住宮崎大幅分散車程更順暢</t>
   </si>
   <si>
+    <t>📌 換算公式：日幣原幣 × 此匯率 ＝ 新台幣（明細表與儀表板自動即時同步）</t>
+  </si>
+  <si>
     <t>行程項目 \ 日期</t>
   </si>
   <si>
@@ -76,6 +91,9 @@
     <t>🚩 當日主題</t>
   </si>
   <si>
+    <t>💰 旅費總支出 (折合 NT$)</t>
+  </si>
+  <si>
     <t>啟程・飛抵熊本市區</t>
   </si>
   <si>
@@ -103,6 +121,9 @@
     <t>桃園機場 ➔ 熊本機場 ➔ 熊本市區</t>
   </si>
   <si>
+    <t>💴 日幣總花費 (¥)</t>
+  </si>
+  <si>
     <t>熊本 ➔ 阿蘇草千里・火山口 ➔ 黑川</t>
   </si>
   <si>
@@ -124,6 +145,9 @@
     <t>🚗 預估車程</t>
   </si>
   <si>
+    <t>👤 每人平均分攤 (NT$)</t>
+  </si>
+  <si>
     <t>無自駕 (機場利木津巴士約 50 分)</t>
   </si>
   <si>
@@ -154,6 +178,9 @@
     <t>🟢 絕佳｜景致壯闊，下午提早進黑川享受秘湯</t>
   </si>
   <si>
+    <t>📝 已記帳筆數</t>
+  </si>
+  <si>
     <t>🟢 良好｜划船提前預約，傍晚沿高速順暢抵達宮崎</t>
   </si>
   <si>
@@ -170,6 +197,9 @@
   </si>
   <si>
     <t>☀️ 上午行程</t>
+  </si>
+  <si>
+    <t>💡 南九州行程記帳小提示</t>
   </si>
   <si>
     <t>• 12:00 抵達桃園機場 T2 辦理報到與托運
@@ -307,16 +337,35 @@
     <t>地雞與蔬菜卷 Torikura 天文館店</t>
   </si>
   <si>
+    <t>1. 雙幣別自由選：明細中幣別選 JPY 即乘匯率換算 NT$，選 TWD 則直接計入台幣。
+2. 靈活勾選分攤：每列勾選實際參與的成員，系統自動按人數均攤，非全員消費也能精準分帳！</t>
+  </si>
+  <si>
     <t>大衆馬肉酒場 三村 熊本下通り店</t>
   </si>
   <si>
     <t>宮崎牛燒肉 犇</t>
   </si>
   <si>
+    <t>👥 4 位成員旅費墊付與應分攤結算看板 (自動計算)</t>
+  </si>
+  <si>
+    <t>📊 行程公費類別支出統計</t>
+  </si>
+  <si>
     <t>鄉土料理</t>
   </si>
   <si>
     <t>豬排與、涮涮鍋。黑豚Fukuya</t>
+  </si>
+  <si>
+    <t>成員姓名</t>
+  </si>
+  <si>
+    <t>代墊總額 (NT$)</t>
+  </si>
+  <si>
+    <t>應分攤金額 (NT$)</t>
   </si>
   <si>
     <t>🌙 夜間亮點</t>
@@ -357,12 +406,21 @@
     <t>熊本市區 (辛島町 / 熊本駅前)</t>
   </si>
   <si>
+    <t>結算差額 (NT$)</t>
+  </si>
+  <si>
+    <t>結算狀態</t>
+  </si>
+  <si>
     <t>黑川溫泉旅館 (一泊二食)</t>
   </si>
   <si>
     <t>宮崎海邊特色民宿</t>
   </si>
   <si>
+    <t>結算動作指引</t>
+  </si>
+  <si>
     <t>鹿兒島市區飯店 (天文館 / 中央駅)</t>
   </si>
   <si>
@@ -375,21 +433,33 @@
     <t>熊本熊周邊小物、阿蘇牛奶零食</t>
   </si>
   <si>
+    <t>費用類別</t>
+  </si>
+  <si>
     <t>黑川入湯手形、溫泉手帕、南小國地酒、阿蘇布丁</t>
   </si>
   <si>
     <t>宮崎芒果點心、青島仙貝、日向夏柑橘製品</t>
   </si>
   <si>
+    <t>類別總計 (NT$)</t>
+  </si>
+  <si>
     <t>薩摩蒸氣屋（烤甜甜圈、霞燒菓子）、鹿兒島輕羹、黑豚肉味噌</t>
   </si>
   <si>
     <t>薩摩切子工藝品、櫻島熔岩燒烤盤、知覽綠茶</t>
   </si>
   <si>
+    <t>支出佔比</t>
+  </si>
+  <si>
     <t>熊本「譽之陣太鼓」、武者返糕點、人吉球磨燒酎、黑亭拉麵包</t>
   </si>
   <si>
+    <t>涵蓋重點項目摘要</t>
+  </si>
+  <si>
     <t>熊本機場免稅店九州限定伴手禮（福砂屋長崎蛋糕、明太子餅乾）</t>
   </si>
   <si>
@@ -399,6 +469,9 @@
     <t>Via Inn Prime Kumamoto</t>
   </si>
   <si>
+    <t>阿純</t>
+  </si>
+  <si>
     <t>溫泉旅館 やまびこ</t>
   </si>
   <si>
@@ -408,15 +481,30 @@
     <t>Perch's Apartment 303</t>
   </si>
   <si>
+    <t>🚗 交通費用</t>
+  </si>
+  <si>
     <t>HOTEL AMANEK Kumamoto</t>
   </si>
   <si>
+    <t>華航機票、8人座租車、ETC過路費、櫻島渡輪、機場Jumbo Taxi</t>
+  </si>
+  <si>
+    <t>阿嚕</t>
+  </si>
+  <si>
     <t>確認住宿價錢</t>
   </si>
   <si>
+    <t>🏨 住宿飯店</t>
+  </si>
+  <si>
     <t>💡 南九州自駕關鍵可行性評估與行車優化建議</t>
   </si>
   <si>
+    <t>黑川溫泉秘湯一泊二食、城山酒店鹿兒島、霧島溫泉鄉、熊本市區飯店</t>
+  </si>
+  <si>
     <t>核心維度</t>
   </si>
   <si>
@@ -429,6 +517,9 @@
     <t>現況分析與潛在風險說明</t>
   </si>
   <si>
+    <t>阿姨</t>
+  </si>
+  <si>
     <t>具體優化對策與行車建議</t>
   </si>
   <si>
@@ -462,6 +553,9 @@
     <t>租車時務必提前勾選加購「雪胎 (Studless Tire)」；隨時查詢阿蘇火山氣體即時燈號；大觀峰風大體感溫度極低，需備妥防風保暖衣物。</t>
   </si>
   <si>
+    <t>🍱 餐飲美食</t>
+  </si>
+  <si>
     <t>高千穗峽划船與夜神樂預約</t>
   </si>
   <si>
@@ -477,6 +571,9 @@
     <t>划船於搭乘日前 1 週（官網整點）開放線上搶票；高千穗夜神樂務必於出發前在觀光協會官網預約門票；車輛建議停第 1 御塩井停車場最便捷。</t>
   </si>
   <si>
+    <t>孫三郎/黑樺牛燒肉、吾愛人黑豚涮涮鍋、初榮牛排/地雞、勝烈亭豬排</t>
+  </si>
+  <si>
     <t>人吉中繼休息與高速快線效益</t>
   </si>
   <si>
@@ -489,6 +586,9 @@
     <t>原草稿標註「熊本 2h11m」為一般道路預估，若連開易疲勞。但中繼安排國寶霧島神宮與人吉鰻魚飯動線極佳。</t>
   </si>
   <si>
+    <t>姨丈</t>
+  </si>
+  <si>
     <t>鹿兒島經霧島至人吉約 1h，人吉至熊本走九州自動車道僅需約 1h15m，大幅縮短行車時間；建議租用 ETC 卡配合 KEP 高速公路 PASS。</t>
   </si>
   <si>
@@ -510,6 +610,9 @@
     <t>📋 出發前必辦清單與官方預約時程表</t>
   </si>
   <si>
+    <t>🎫 體驗門票</t>
+  </si>
+  <si>
     <t>預約項目</t>
   </si>
   <si>
@@ -534,9 +637,15 @@
     <t>Toyota / Times / ORIX 等租車網</t>
   </si>
   <si>
+    <t>高千穗夜神樂入場券、指宿砂蒸天然黑砂浴、熊本城天守閣、成趣園</t>
+  </si>
+  <si>
     <t>務必備註「スタッドレスタイヤ (雪胎)」，阿蘇黑川冬季必備；確認含 ETC 機與免責保險。</t>
   </si>
   <si>
+    <t>合計 / 平衡檢查</t>
+  </si>
+  <si>
     <t>⏳ 待確認</t>
   </si>
   <si>
@@ -579,6 +688,9 @@
     <t>冬季為黑川竹燈祭旺季，房間數少，建議儘早鎖定心儀溫泉旅館。</t>
   </si>
   <si>
+    <t>🛍️ 購物採買</t>
+  </si>
+  <si>
     <t>行前文件：VJW 與駕照</t>
   </si>
   <si>
@@ -594,6 +706,9 @@
     <t>⏳ 待辦理</t>
   </si>
   <si>
+    <t>鶴屋百貨/下通商店街、櫻之馬場土產伴手禮、超市水果零食</t>
+  </si>
+  <si>
     <t>名店用餐：人吉鰻魚 / 壽庵</t>
   </si>
   <si>
@@ -604,121 +719,6 @@
   </si>
   <si>
     <t>上村うなぎや建議 11:00 前抵達；鹿兒島壽庵中央駅店或天文館店建議先線上訂位。</t>
-  </si>
-  <si>
-    <t>🇯🇵 2026 南九州家族之旅 • 4人旅費分攤結算系統</t>
-  </si>
-  <si>
-    <t>💱 日幣匯率 (JPY➔TWD)</t>
-  </si>
-  <si>
-    <t>（可依即時牌告修改）</t>
-  </si>
-  <si>
-    <t>📅 2026/12/22 ~ 12/28（7天6夜） ｜ 👥 家族成員 4 位 ｜ 💡 支援日幣/台幣雙幣自動折算與即時多方代墊平分</t>
-  </si>
-  <si>
-    <t>📌 換算公式：日幣原幣 × 此匯率 ＝ 新台幣（明細表與儀表板自動即時同步）</t>
-  </si>
-  <si>
-    <t>💰 旅費總支出 (折合 NT$)</t>
-  </si>
-  <si>
-    <t>💴 日幣總花費 (¥)</t>
-  </si>
-  <si>
-    <t>👤 每人平均分攤 (NT$)</t>
-  </si>
-  <si>
-    <t>📝 已記帳筆數</t>
-  </si>
-  <si>
-    <t>💡 南九州行程記帳小提示</t>
-  </si>
-  <si>
-    <t>1. 雙幣別自由選：明細中幣別選 JPY 即乘匯率換算 NT$，選 TWD 則直接計入台幣。
-2. 靈活勾選分攤：每列勾選實際參與的成員，系統自動按人數均攤，非全員消費也能精準分帳！</t>
-  </si>
-  <si>
-    <t>👥 4 位成員旅費墊付與應分攤結算看板 (自動計算)</t>
-  </si>
-  <si>
-    <t>📊 行程公費類別支出統計</t>
-  </si>
-  <si>
-    <t>成員姓名</t>
-  </si>
-  <si>
-    <t>代墊總額 (NT$)</t>
-  </si>
-  <si>
-    <t>應分攤金額 (NT$)</t>
-  </si>
-  <si>
-    <t>結算差額 (NT$)</t>
-  </si>
-  <si>
-    <t>結算狀態</t>
-  </si>
-  <si>
-    <t>結算動作指引</t>
-  </si>
-  <si>
-    <t>費用類別</t>
-  </si>
-  <si>
-    <t>類別總計 (NT$)</t>
-  </si>
-  <si>
-    <t>支出佔比</t>
-  </si>
-  <si>
-    <t>涵蓋重點項目摘要</t>
-  </si>
-  <si>
-    <t>阿純</t>
-  </si>
-  <si>
-    <t>🚗 交通費用</t>
-  </si>
-  <si>
-    <t>華航機票、8人座租車、ETC過路費、櫻島渡輪、機場Jumbo Taxi</t>
-  </si>
-  <si>
-    <t>阿嚕</t>
-  </si>
-  <si>
-    <t>🏨 住宿飯店</t>
-  </si>
-  <si>
-    <t>黑川溫泉秘湯一泊二食、城山酒店鹿兒島、霧島溫泉鄉、熊本市區飯店</t>
-  </si>
-  <si>
-    <t>阿姨</t>
-  </si>
-  <si>
-    <t>🍱 餐飲美食</t>
-  </si>
-  <si>
-    <t>孫三郎/黑樺牛燒肉、吾愛人黑豚涮涮鍋、初榮牛排/地雞、勝烈亭豬排</t>
-  </si>
-  <si>
-    <t>姨丈</t>
-  </si>
-  <si>
-    <t>🎫 體驗門票</t>
-  </si>
-  <si>
-    <t>高千穗夜神樂入場券、指宿砂蒸天然黑砂浴、熊本城天守閣、成趣園</t>
-  </si>
-  <si>
-    <t>合計 / 平衡檢查</t>
-  </si>
-  <si>
-    <t>🛍️ 購物採買</t>
-  </si>
-  <si>
-    <t>鶴屋百貨/下通商店街、櫻之馬場土產伴手禮、超市水果零食</t>
   </si>
   <si>
     <t>💡 結算指引：由應補款成員直接匯款補給多代墊成員，全數付清後即完成平帳。</t>
@@ -828,87 +828,6 @@
     <font/>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FF1F3529"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FF364A3E"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color rgb="FF161D18"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FF161D18"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FF246A4A"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FF33260C"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color theme="1"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFF0000"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
-      <b/>
       <sz val="16.0"/>
       <color rgb="FF1F395F"/>
       <name val="Google Sans"/>
@@ -921,6 +840,18 @@
     </font>
     <font>
       <b/>
+      <sz val="10.0"/>
+      <color rgb="FF1F3529"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FF364A3E"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12.0"/>
       <color rgb="FF1F395F"/>
       <name val="Google Sans"/>
@@ -928,6 +859,11 @@
     <font>
       <sz val="9.0"/>
       <color rgb="FF74777E"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF161D18"/>
       <name val="Google Sans"/>
     </font>
     <font>
@@ -946,8 +882,25 @@
     </font>
     <font>
       <b/>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FF161D18"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9.0"/>
       <color rgb="FF1F395F"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
       <name val="Google Sans"/>
     </font>
     <font>
@@ -958,14 +911,31 @@
     </font>
     <font>
       <b/>
+      <sz val="10.0"/>
+      <color rgb="FF246A4A"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9.0"/>
       <color rgb="FF0C592D"/>
       <name val="Google Sans"/>
     </font>
     <font>
       <b/>
+      <sz val="10.0"/>
+      <color rgb="FF33260C"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9.0"/>
       <color rgb="FF724C0C"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color theme="1"/>
       <name val="Google Sans"/>
     </font>
     <font>
@@ -978,6 +948,12 @@
       <b/>
       <sz val="14.0"/>
       <color rgb="FF263F66"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF0000FF"/>
       <name val="Google Sans"/>
     </font>
     <font>
@@ -998,6 +974,12 @@
       <name val="Google Sans"/>
     </font>
     <font>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <name val="Google Sans"/>
@@ -1005,6 +987,24 @@
     <font>
       <b/>
       <color theme="1"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Google Sans"/>
     </font>
     <font>
@@ -1033,6 +1033,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2FF"/>
+        <bgColor rgb="FFD4E2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD0E8D6"/>
         <bgColor rgb="FFD0E8D6"/>
       </patternFill>
@@ -1045,50 +1051,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FF"/>
+        <bgColor rgb="FFF7F9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5FAF4"/>
-        <bgColor rgb="FFF5FAF4"/>
+        <fgColor rgb="FFF2F4F9"/>
+        <bgColor rgb="FFF2F4F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAF8EB"/>
-        <bgColor rgb="FFFAF8EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE5CD"/>
-        <bgColor rgb="FFFCE5CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2FF"/>
-        <bgColor rgb="FFD4E2FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7F9FF"/>
-        <bgColor rgb="FFF7F9FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F4F9"/>
-        <bgColor rgb="FFF2F4F9"/>
+        <fgColor rgb="FFF5FAF4"/>
+        <bgColor rgb="FFF5FAF4"/>
       </patternFill>
     </fill>
     <fill>
@@ -1101,6 +1083,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD8EDE0"/>
         <bgColor rgb="FFD8EDE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAF8EB"/>
+        <bgColor rgb="FFFAF8EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -1149,6 +1137,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF3D5F90"/>
         <bgColor rgb="FF3D5F90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor rgb="FFFCE5CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -1204,6 +1204,20 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3D5F90"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3D5F90"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3D5F90"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3D5F90"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFC4D1C6"/>
       </left>
       <right style="thin">
@@ -1214,20 +1228,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFC4D1C6"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3D5F90"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3D5F90"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3D5F90"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3D5F90"/>
       </bottom>
     </border>
     <border>
@@ -1562,156 +1562,96 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="7" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="10" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="7" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="7" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="9" fillId="11" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="12" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="13" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="7" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="14" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="15" fillId="15" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="17" fillId="16" fontId="24" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="18" fillId="17" fontId="26" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="19" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="19" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="20" fillId="18" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="11" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="10" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="13" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="14" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="15" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="16" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="17" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="18" fontId="29" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="19" fontId="30" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="20" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="21" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="21" fillId="19" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="22" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1725,112 +1665,172 @@
     <xf borderId="30" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="31" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="32" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="33" fillId="22" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="9" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="33" fillId="20" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="34" fillId="22" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="34" fillId="20" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="35" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="7" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="36" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="33" fillId="0" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="21" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="21" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="22" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="34" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="33" fillId="0" fontId="31" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="33" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="34" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="34" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="21" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="33" fillId="0" fontId="10" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="34" fillId="0" fontId="32" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="33" fillId="5" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="34" fillId="0" fontId="28" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="7" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="33" fillId="5" fontId="21" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="33" fillId="7" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="33" fillId="5" fontId="34" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="7" fontId="31" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="33" fillId="5" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="7" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="34" fillId="5" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="9" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="34" fillId="7" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="33" fillId="23" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="23" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="33" fillId="23" fontId="34" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="23" fontId="31" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="34" fillId="23" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="34" fillId="23" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="34" fillId="24" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="25" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="25" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="22" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="20" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="37" fillId="25" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="37" fillId="25" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="18" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="38" fillId="16" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="18" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="38" fillId="16" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="18" fontId="21" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="38" fillId="16" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="18" fontId="34" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="38" fillId="16" fontId="31" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="18" fontId="21" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="38" fillId="16" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="39" fillId="18" fontId="23" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="39" fillId="16" fontId="12" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="0" fontId="21" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="38" fillId="0" fontId="10" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="38" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="38" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="0" fontId="21" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="38" fillId="0" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="0" fontId="34" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="38" fillId="0" fontId="31" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="0" fontId="21" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="38" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="39" fillId="0" fontId="23" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="39" fillId="0" fontId="12" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="38" fillId="18" fontId="21" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="38" fillId="16" fontId="10" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="23" fontId="36" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -1839,16 +1839,16 @@
     <xf borderId="0" fillId="23" fontId="36" numFmtId="169" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="23" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="23" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="23" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="23" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="23" fontId="36" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="37" fillId="23" fontId="23" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="37" fillId="23" fontId="12" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2109,11 +2109,11 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
+      <c r="H1" s="4"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
+      <c r="A2" s="6" t="s">
+        <v>3</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2121,443 +2121,443 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
+      <c r="H2" s="4"/>
     </row>
     <row r="3" ht="21.0" hidden="1" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="5" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" ht="19.5" hidden="1" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="6" t="s">
+      <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" ht="27.0" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="A5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="B5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="C5" s="14" t="s">
         <v>17</v>
       </c>
+      <c r="D5" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="A6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="9" t="s">
+      <c r="B6" s="16" t="s">
         <v>25</v>
       </c>
+      <c r="C6" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="10" t="s">
+      <c r="A7" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="B7" s="19" t="s">
         <v>33</v>
       </c>
+      <c r="C7" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="11" t="s">
+      <c r="A8" s="15" t="s">
         <v>41</v>
       </c>
+      <c r="B8" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>49</v>
+      <c r="A9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>57</v>
+      <c r="A10" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>65</v>
+      <c r="A11" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>73</v>
+      <c r="A12" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>81</v>
+      <c r="A13" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>96</v>
+      <c r="A17" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>102</v>
+      <c r="A18" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>110</v>
+      <c r="A19" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="H19" s="56" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="H20" s="21"/>
+      <c r="A20" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="H20" s="67"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22">
+      <c r="A21" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68">
         <v>14206.0</v>
       </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="23">
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="69">
         <f>sum(B21:G21)</f>
         <v>14206</v>
       </c>
     </row>
     <row r="22" ht="27.0" customHeight="1">
-      <c r="A22" s="24" t="s">
-        <v>118</v>
+      <c r="A22" s="70" t="s">
+        <v>146</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2565,141 +2565,141 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>122</v>
+      <c r="A23" s="71" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="71" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="71" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H23" s="3"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" ht="48.75" customHeight="1">
-      <c r="A24" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="B24" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>127</v>
+      <c r="A24" s="74" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="75" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="76" t="s">
+        <v>157</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="H24" s="3"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" ht="48.75" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>132</v>
+      <c r="A25" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" s="81" t="s">
+        <v>162</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="H25" s="3"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" ht="48.75" customHeight="1">
-      <c r="A26" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>137</v>
+      <c r="A26" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="75" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="75" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="76" t="s">
+        <v>168</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="H26" s="3"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="76" t="s">
+        <v>169</v>
+      </c>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" ht="48.75" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>142</v>
+      <c r="A27" s="78" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" s="80" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" s="80" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" s="81" t="s">
+        <v>174</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="H27" s="3"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="81" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" ht="48.75" customHeight="1">
-      <c r="A28" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>147</v>
+      <c r="A28" s="74" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="75" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="75" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="76" t="s">
+        <v>180</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="H28" s="3"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
+      <c r="A29" s="68"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
     </row>
     <row r="30" ht="27.0" customHeight="1">
-      <c r="A30" s="24" t="s">
-        <v>149</v>
+      <c r="A30" s="70" t="s">
+        <v>182</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2707,157 +2707,157 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="3"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>153</v>
+      <c r="A31" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" s="71" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" s="71" t="s">
+        <v>186</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H31" s="3"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" ht="33.75" customHeight="1">
-      <c r="A32" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>158</v>
+      <c r="A32" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="B32" s="75" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" s="75" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="83" t="s">
+        <v>193</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="H32" s="3"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="85" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" ht="33.75" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="B33" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="D33" s="34" t="s">
-        <v>163</v>
+      <c r="A33" s="78" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" s="80" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" s="80" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" s="86" t="s">
+        <v>199</v>
       </c>
       <c r="E33" s="2"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="H33" s="3"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="88" t="s">
+        <v>200</v>
+      </c>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" ht="33.75" customHeight="1">
-      <c r="A34" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>168</v>
+      <c r="A34" s="74" t="s">
+        <v>201</v>
+      </c>
+      <c r="B34" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="C34" s="75" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" s="83" t="s">
+        <v>204</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="H34" s="3"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="85" t="s">
+        <v>200</v>
+      </c>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" ht="33.75" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="B35" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>172</v>
+      <c r="A35" s="78" t="s">
+        <v>205</v>
+      </c>
+      <c r="B35" s="80" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="D35" s="86" t="s">
+        <v>208</v>
       </c>
       <c r="E35" s="2"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="H35" s="3"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="88" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" ht="33.75" customHeight="1">
-      <c r="A36" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="B36" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C36" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>176</v>
+      <c r="A36" s="74" t="s">
+        <v>210</v>
+      </c>
+      <c r="B36" s="75" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" s="83" t="s">
+        <v>213</v>
       </c>
       <c r="E36" s="2"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="H36" s="3"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="85" t="s">
+        <v>214</v>
+      </c>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" ht="33.75" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="B37" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="D37" s="34" t="s">
-        <v>181</v>
+      <c r="A37" s="78" t="s">
+        <v>216</v>
+      </c>
+      <c r="B37" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" s="80" t="s">
+        <v>218</v>
+      </c>
+      <c r="D37" s="86" t="s">
+        <v>219</v>
       </c>
       <c r="E37" s="2"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="H37" s="3"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="88" t="s">
+        <v>200</v>
+      </c>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
+      <c r="A38" s="68"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="68"/>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
@@ -3909,365 +3909,365 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="28.5" customHeight="1">
-      <c r="B2" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="K2" s="38">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="8">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLEFINANCE(""CURRENCY:JPYTWD"")"),0.2077359)</f>
         <v>0.2077359</v>
       </c>
-      <c r="L2" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
+      <c r="L2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="B3" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>186</v>
-      </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
+      <c r="B3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
     </row>
     <row r="4" ht="7.5" customHeight="1">
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" ht="18.0" customHeight="1">
-      <c r="B5" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="47"/>
-      <c r="G5" s="48" t="s">
-        <v>190</v>
-      </c>
-      <c r="H5" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
+      <c r="B5" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="G5" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
     </row>
     <row r="6" ht="18.0" customHeight="1">
-      <c r="B6" s="52">
+      <c r="B6" s="31">
         <f>H42</f>
         <v>71250.06</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="54">
+      <c r="C6" s="32"/>
+      <c r="D6" s="33">
         <f>SUMIF(F18:F41, "JPY", G18:G41)</f>
         <v>113201</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="35">
         <f>IFERROR(ROUND(B6/4, 0), 0)</f>
         <v>17813</v>
       </c>
-      <c r="F6" s="56"/>
-      <c r="G6" s="57" t="str">
+      <c r="F6" s="36"/>
+      <c r="G6" s="37" t="str">
         <f>COUNTA(C18:C41)&amp;" 筆"</f>
         <v>6 筆</v>
       </c>
-      <c r="H6" s="58" t="s">
-        <v>192</v>
-      </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
+      <c r="H6" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="B7" s="61"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
     </row>
     <row r="8" ht="21.0" customHeight="1">
-      <c r="B8" s="70" t="s">
-        <v>193</v>
-      </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
+      <c r="B8" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="71" t="s">
-        <v>195</v>
-      </c>
-      <c r="C9" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" s="71" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" s="71" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" s="71" t="s">
-        <v>199</v>
-      </c>
-      <c r="G9" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="H9" s="73"/>
-      <c r="I9" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="J9" s="71" t="s">
-        <v>202</v>
-      </c>
-      <c r="K9" s="71" t="s">
-        <v>203</v>
-      </c>
-      <c r="L9" s="72" t="s">
-        <v>204</v>
-      </c>
-      <c r="M9" s="74"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
+      <c r="B9" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="55"/>
+      <c r="I9" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="K9" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="L9" s="54" t="s">
+        <v>132</v>
+      </c>
+      <c r="M9" s="57"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="75" t="s">
-        <v>205</v>
-      </c>
-      <c r="C10" s="76">
+      <c r="B10" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="61">
         <f t="shared" ref="C10:C13" si="1">SUMIF($E$18:$E$99, B10, $H$18:$H$99)</f>
         <v>47775</v>
       </c>
-      <c r="D10" s="76">
+      <c r="D10" s="61">
         <f>SUMIF(I$18:I$99, TRUE, $N$18:$N$99)</f>
         <v>20575.015</v>
       </c>
-      <c r="E10" s="77">
+      <c r="E10" s="62">
         <f t="shared" ref="E10:E13" si="2">C10-D10</f>
         <v>27199.985</v>
       </c>
-      <c r="F10" s="78" t="str">
+      <c r="F10" s="63" t="str">
         <f t="shared" ref="F10:F13" si="3">IF(E10&gt;0, "🟢 應收款（多墊）", IF(E10&lt;0, "🔴 應補款（少付）", "⚪ 結清"))</f>
         <v>🟢 應收款（多墊）</v>
       </c>
-      <c r="G10" s="79" t="str">
+      <c r="G10" s="64" t="str">
         <f t="shared" ref="G10:G13" si="4">IF(E10&gt;0, "由其他人補給 "&amp;B10&amp;" NT$ "&amp;TEXT(E10, "#,##0"), IF(E10&lt;0, B10&amp;" 應支付 NT$ "&amp;TEXT(ABS(E10), "#,##0"), "已結清無須退補"))</f>
         <v>由其他人補給 阿純 NT$ 27,200</v>
       </c>
-      <c r="H10" s="73"/>
-      <c r="I10" s="78" t="s">
-        <v>206</v>
-      </c>
-      <c r="J10" s="76">
+      <c r="H10" s="55"/>
+      <c r="I10" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="J10" s="61">
         <f>SUMIF($D$18:$D$41, "交通", $H$18:$H$41)</f>
         <v>33150</v>
       </c>
-      <c r="K10" s="80">
+      <c r="K10" s="65">
         <f t="shared" ref="K10:K15" si="5">IFERROR(J10/$B$6, 0)</f>
         <v>0.4652627661</v>
       </c>
-      <c r="L10" s="81" t="s">
-        <v>207</v>
-      </c>
-      <c r="M10" s="74"/>
-      <c r="N10" s="73"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
+      <c r="L10" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="M10" s="57"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="75" t="s">
-        <v>208</v>
-      </c>
-      <c r="C11" s="76">
+      <c r="B11" s="59" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="61">
         <f t="shared" si="1"/>
         <v>23475.06</v>
       </c>
-      <c r="D11" s="76">
+      <c r="D11" s="61">
         <f>SUMIF(J$18:J$99, TRUE, $N$18:$N$99)</f>
         <v>9525.015</v>
       </c>
-      <c r="E11" s="77">
+      <c r="E11" s="62">
         <f t="shared" si="2"/>
         <v>13950.045</v>
       </c>
-      <c r="F11" s="78" t="str">
+      <c r="F11" s="63" t="str">
         <f t="shared" si="3"/>
         <v>🟢 應收款（多墊）</v>
       </c>
-      <c r="G11" s="79" t="str">
+      <c r="G11" s="64" t="str">
         <f t="shared" si="4"/>
         <v>由其他人補給 阿嚕 NT$ 13,950</v>
       </c>
-      <c r="H11" s="73"/>
-      <c r="I11" s="78" t="s">
-        <v>209</v>
-      </c>
-      <c r="J11" s="76">
+      <c r="H11" s="55"/>
+      <c r="I11" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="J11" s="61">
         <f>SUMIF($D$18:$D$41, "住宿", $H$18:$H$41)</f>
         <v>38100.06</v>
       </c>
-      <c r="K11" s="80">
+      <c r="K11" s="65">
         <f t="shared" si="5"/>
         <v>0.5347372339</v>
       </c>
-      <c r="L11" s="81" t="s">
-        <v>210</v>
-      </c>
-      <c r="M11" s="74"/>
-      <c r="N11" s="73"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
+      <c r="L11" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="M11" s="57"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="82" t="s">
-        <v>211</v>
-      </c>
-      <c r="C12" s="83">
+      <c r="B12" s="72" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D12" s="83">
+      <c r="D12" s="73">
         <f>SUMIF(K$18:K$99, TRUE, $N$18:$N$99)</f>
         <v>20575.015</v>
       </c>
-      <c r="E12" s="84">
+      <c r="E12" s="77">
         <f t="shared" si="2"/>
         <v>-20575.015</v>
       </c>
-      <c r="F12" s="85" t="str">
+      <c r="F12" s="79" t="str">
         <f t="shared" si="3"/>
         <v>🔴 應補款（少付）</v>
       </c>
-      <c r="G12" s="86" t="str">
+      <c r="G12" s="82" t="str">
         <f t="shared" si="4"/>
         <v>阿姨 應支付 NT$ 20,575</v>
       </c>
-      <c r="H12" s="73"/>
-      <c r="I12" s="78" t="s">
-        <v>212</v>
-      </c>
-      <c r="J12" s="76">
+      <c r="H12" s="55"/>
+      <c r="I12" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="J12" s="61">
         <f>SUMIF($D$18:$D$41, "餐飲", $H$18:$H$41)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="80">
+      <c r="K12" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L12" s="81" t="s">
-        <v>213</v>
-      </c>
-      <c r="M12" s="74"/>
-      <c r="N12" s="73"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
+      <c r="L12" s="66" t="s">
+        <v>170</v>
+      </c>
+      <c r="M12" s="57"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="B13" s="82" t="s">
-        <v>214</v>
-      </c>
-      <c r="C13" s="83">
+      <c r="B13" s="72" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D13" s="83">
+      <c r="D13" s="73">
         <f>SUMIF(L$18:L$99, TRUE, $N$18:$N$99)</f>
         <v>20575.015</v>
       </c>
-      <c r="E13" s="84">
+      <c r="E13" s="77">
         <f t="shared" si="2"/>
         <v>-20575.015</v>
       </c>
-      <c r="F13" s="85" t="str">
+      <c r="F13" s="79" t="str">
         <f t="shared" si="3"/>
         <v>🔴 應補款（少付）</v>
       </c>
-      <c r="G13" s="86" t="str">
+      <c r="G13" s="82" t="str">
         <f t="shared" si="4"/>
         <v>姨丈 應支付 NT$ 20,575</v>
       </c>
-      <c r="H13" s="73"/>
-      <c r="I13" s="78" t="s">
-        <v>215</v>
-      </c>
-      <c r="J13" s="76">
+      <c r="H13" s="55"/>
+      <c r="I13" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="J13" s="61">
         <f>SUMIF($D$18:$D$41, "體驗門票", $H$18:$H$41)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="80">
+      <c r="K13" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L13" s="81" t="s">
-        <v>216</v>
-      </c>
-      <c r="M13" s="74"/>
-      <c r="N13" s="73"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
+      <c r="L13" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="M13" s="57"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="87" t="s">
-        <v>217</v>
-      </c>
-      <c r="C14" s="88">
+      <c r="B14" s="84" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="87">
         <f t="shared" ref="C14:E14" si="6">SUM(C10:C13)</f>
         <v>71250.06</v>
       </c>
-      <c r="D14" s="88">
+      <c r="D14" s="87">
         <f t="shared" si="6"/>
         <v>71250.06</v>
       </c>
-      <c r="E14" s="88">
+      <c r="E14" s="87">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F14" s="87" t="str">
+      <c r="F14" s="84" t="str">
         <f>IF(ABS(E14)&lt;=5, "✅ 收支平衡", "⚠️ 差額未平")</f>
         <v>✅ 收支平衡</v>
       </c>
@@ -4275,71 +4275,71 @@
         <f>IF(ABS(C14-D14)&lt;=5, "帳目完全平衡 (差額 0)", "存在未平差額，請檢查明細")</f>
         <v>帳目完全平衡 (差額 0)</v>
       </c>
-      <c r="H14" s="73"/>
-      <c r="I14" s="78" t="s">
-        <v>218</v>
-      </c>
-      <c r="J14" s="76">
+      <c r="H14" s="55"/>
+      <c r="I14" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="J14" s="61">
         <f>SUMIF($D$18:$D$41, "購物", $H$18:$H$41)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="80">
+      <c r="K14" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L14" s="81" t="s">
-        <v>219</v>
-      </c>
-      <c r="M14" s="74"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
+      <c r="L14" s="66" t="s">
+        <v>215</v>
+      </c>
+      <c r="M14" s="57"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="90" t="s">
         <v>220</v>
       </c>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="78" t="s">
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="63" t="s">
         <v>221</v>
       </c>
-      <c r="J15" s="76">
+      <c r="J15" s="61">
         <f>SUMIF($D$18:$D$41, "雜支", $H$18:$H$41)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="80">
+      <c r="K15" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L15" s="81" t="s">
+      <c r="L15" s="66" t="s">
         <v>222</v>
       </c>
-      <c r="M15" s="74"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
     </row>
     <row r="16" ht="7.5" customHeight="1">
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
     </row>
     <row r="17" ht="24.0" customHeight="1">
       <c r="B17" s="91" t="s">
@@ -4349,7 +4349,7 @@
         <v>224</v>
       </c>
       <c r="D17" s="91" t="s">
-        <v>201</v>
+        <v>124</v>
       </c>
       <c r="E17" s="91" t="s">
         <v>225</v>
@@ -4400,7 +4400,7 @@
         <v>234</v>
       </c>
       <c r="E18" s="94" t="s">
-        <v>205</v>
+        <v>136</v>
       </c>
       <c r="F18" s="94" t="s">
         <v>235</v>
@@ -4442,13 +4442,13 @@
         <v>46378.0</v>
       </c>
       <c r="C19" s="101" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D19" s="102" t="s">
         <v>237</v>
       </c>
       <c r="E19" s="102" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="F19" s="102" t="s">
         <v>238</v>
@@ -4493,7 +4493,7 @@
         <v>237</v>
       </c>
       <c r="E20" s="102" t="s">
-        <v>205</v>
+        <v>136</v>
       </c>
       <c r="F20" s="102" t="s">
         <v>238</v>
@@ -4538,7 +4538,7 @@
         <v>237</v>
       </c>
       <c r="E21" s="102" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="F21" s="102" t="s">
         <v>235</v>
@@ -4577,13 +4577,13 @@
         <v>241</v>
       </c>
       <c r="C22" s="95" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="D22" s="94" t="s">
         <v>237</v>
       </c>
       <c r="E22" s="94" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="F22" s="94" t="s">
         <v>235</v>
@@ -4622,13 +4622,13 @@
         <v>46383.0</v>
       </c>
       <c r="C23" s="95" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D23" s="94" t="s">
         <v>237</v>
       </c>
       <c r="E23" s="94" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="F23" s="94" t="s">
         <v>238</v>
@@ -5288,21 +5288,21 @@
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="40"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="40"/>
-      <c r="K43" s="40"/>
-      <c r="L43" s="40"/>
-      <c r="M43" s="40"/>
-      <c r="N43" s="40"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="40"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>
